--- a/Documents/ログイン画面設計書詳細クラス図.xlsx
+++ b/Documents/ログイン画面設計書詳細クラス図.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C55CED-FD16-4F04-A3D3-BABCA3C2405E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F6799F-2660-410B-B843-7B62EF8938E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{E17775E1-5AD2-4F47-B92A-D4F1BD400720}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>備考</t>
   </si>
@@ -195,6 +195,10 @@
     <rPh sb="8" eb="11">
       <t>ミニュウリョク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1443,6 +1447,273 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>90414</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>4295</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93BC5F51-FAA9-7E77-8E6F-00F88E80736E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2552700" y="1114425"/>
+          <a:ext cx="3024114" cy="775820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>923925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>41472</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CAACC62-08E7-30C0-94C5-615579F4DE38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="857250" y="2867025"/>
+          <a:ext cx="3324225" cy="2622747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11699</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>94687</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B772A5BB-4E77-4C0D-1A63-9BD136AD0460}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4419600" y="2869199"/>
+          <a:ext cx="3314700" cy="1216463"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>771525</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="コネクタ: カギ線 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FB6F42D-A920-6C89-3CAE-D1E692422A1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="2895600" y="1895475"/>
+          <a:ext cx="971550" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28578</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="コネクタ: カギ線 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF0AFD51-B806-7AD3-8E07-CF6F0593BDA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipV="1">
+          <a:off x="4324351" y="1943101"/>
+          <a:ext cx="1000126" cy="847722"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2052,7 +2323,9 @@
       <c r="E19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="G19" s="4" t="s">
         <v>27</v>
       </c>
@@ -4544,5 +4817,6 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>